--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.95539206655555</v>
+        <v>3.730251210815278</v>
       </c>
       <c r="D2" t="n">
-        <v>16.02875216008107</v>
+        <v>2.604672226013174</v>
       </c>
       <c r="E2" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F2" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.20982590417056</v>
+        <v>5.721596709427717</v>
       </c>
       <c r="D3" t="n">
-        <v>35.16036961171775</v>
+        <v>5.713560061904135</v>
       </c>
       <c r="E3" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F3" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.19042088194662</v>
+        <v>3.930943393316326</v>
       </c>
       <c r="D4" t="n">
-        <v>24.13587354419385</v>
+        <v>3.9220794509315</v>
       </c>
       <c r="E4" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F4" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.67928055649534</v>
+        <v>5.635383090430493</v>
       </c>
       <c r="D5" t="n">
-        <v>35.30637181555871</v>
+        <v>5.737285420028291</v>
       </c>
       <c r="E5" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F5" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.87379190055197</v>
+        <v>4.854491183839696</v>
       </c>
       <c r="D6" t="n">
-        <v>20.55966238937426</v>
+        <v>3.340945138273317</v>
       </c>
       <c r="E6" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F6" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.02977170778503</v>
+        <v>3.742337902515068</v>
       </c>
       <c r="D7" t="n">
-        <v>22.99882655317261</v>
+        <v>3.73730931489055</v>
       </c>
       <c r="E7" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F7" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.4539464499113</v>
+        <v>5.111266298110587</v>
       </c>
       <c r="D8" t="n">
-        <v>31.50004117227225</v>
+        <v>5.118756690494241</v>
       </c>
       <c r="E8" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F8" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.77820099704019</v>
+        <v>6.626457662019032</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82861299066468</v>
+        <v>6.63464961098301</v>
       </c>
       <c r="E9" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F9" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.18700337170647</v>
+        <v>7.505388047902303</v>
       </c>
       <c r="D10" t="n">
-        <v>46.24070368512515</v>
+        <v>7.514114348832837</v>
       </c>
       <c r="E10" t="n">
-        <v>7.629428275993853</v>
+        <v>1.239782094849001</v>
       </c>
       <c r="F10" t="n">
-        <v>9.457100016924393</v>
+        <v>1.536778752750214</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
